--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_6.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_6.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>DV</t>
+          <t>Sessions</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RiskTaking</t>
+          <t>IV</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.579178727535796</v>
+        <v>-1.479937726708124</v>
       </c>
       <c r="C2">
-        <v>0.4326309551980703</v>
+        <v>-1.33920285134401</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6096209260889942</v>
+        <v>-0.3122754453981268</v>
       </c>
       <c r="C3">
-        <v>-0.4356492332566894</v>
+        <v>0.7044203768748741</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8247596878317935</v>
+        <v>-0.08260085827629328</v>
       </c>
       <c r="C4">
-        <v>0.05176493237517791</v>
+        <v>0.08827931415102264</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-1.12737203813792</v>
+        <v>0.06749133645921733</v>
       </c>
       <c r="C5">
-        <v>-1.214419166081919</v>
+        <v>1.62004920305427</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.7634997339499963</v>
+        <v>-0.3870439522769767</v>
       </c>
       <c r="C6">
-        <v>0.8312822417613678</v>
+        <v>0.6643853893751863</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.7165363618730237</v>
+        <v>-0.5303066545216221</v>
       </c>
       <c r="C7">
-        <v>-0.04328092933947617</v>
+        <v>0.6927461191474594</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.741372479929169</v>
+        <v>0.702581056546307</v>
       </c>
       <c r="C8">
-        <v>-0.8791730292417039</v>
+        <v>0.2472729584330373</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.2267111946929928</v>
+        <v>-0.07281366889414355</v>
       </c>
       <c r="C9">
-        <v>1.51452462022213</v>
+        <v>1.097878002973717</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.08985777853351457</v>
+        <v>0.8432433991927896</v>
       </c>
       <c r="C10">
-        <v>0.7153725912060678</v>
+        <v>0.3028063258067368</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.925857245294879</v>
+        <v>-1.0998503402057</v>
       </c>
       <c r="C11">
-        <v>1.640680218763339</v>
+        <v>0.7408424058431846</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.3908882114481512</v>
+        <v>0.3904211225663359</v>
       </c>
       <c r="C12">
-        <v>-2.758059548598822</v>
+        <v>-0.0965251036655641</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.08102871790413528</v>
+        <v>0.4137074557784746</v>
       </c>
       <c r="C13">
-        <v>0.9899216859235225</v>
+        <v>0.5154221187187807</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>2.184169163374767</v>
+        <v>0.3153765104769584</v>
       </c>
       <c r="C14">
-        <v>-0.9400857697477638</v>
+        <v>0.3320004593374042</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.2095596938970404</v>
+        <v>0.8605543568284977</v>
       </c>
       <c r="C15">
-        <v>-1.91075913500687</v>
+        <v>1.676571944737384</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>2.032857516413648</v>
+        <v>0.4560129617618299</v>
       </c>
       <c r="C16">
-        <v>1.124036310911139</v>
+        <v>1.160512183031754</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.1937403681373429</v>
+        <v>-0.4048497745070206</v>
       </c>
       <c r="C17">
-        <v>-0.8315250615607104</v>
+        <v>1.13777217725619</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.001958969521215952</v>
+        <v>-0.1981394635425152</v>
       </c>
       <c r="C18">
-        <v>0.5358441292722196</v>
+        <v>2.177635561223976</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.07676530423001462</v>
+        <v>-1.228437157135956</v>
       </c>
       <c r="C19">
-        <v>-1.150568365717874</v>
+        <v>-0.4830111549910109</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>2.028924212947809</v>
+        <v>-0.7243961428698691</v>
       </c>
       <c r="C20">
-        <v>0.4914849791681004</v>
+        <v>1.200670175234036</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.2884293270745855</v>
+        <v>-0.7122230624845655</v>
       </c>
       <c r="C21">
-        <v>0.2932709854898411</v>
+        <v>-1.368811097682494</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.849575978684296</v>
+        <v>-0.3348491378239326</v>
       </c>
       <c r="C22">
-        <v>0.7943468700665673</v>
+        <v>-1.029374490998008</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.01583125526977062</v>
+        <v>1.538365162517632</v>
       </c>
       <c r="C23">
-        <v>-2.382474788900712</v>
+        <v>-0.2888084218297122</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.7599768719485935</v>
+        <v>-0.1561960934341856</v>
       </c>
       <c r="C24">
-        <v>-0.006928861744164424</v>
+        <v>-0.4261414509578801</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.2190423586553157</v>
+        <v>0.4373234928972479</v>
       </c>
       <c r="C25">
-        <v>0.4262071665631116</v>
+        <v>-1.444475082735836</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.22565736253878</v>
+        <v>0.2256128672726063</v>
       </c>
       <c r="C26">
-        <v>-1.332965152276982</v>
+        <v>1.818418183460937</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.1109229033109363</v>
+        <v>-0.9727362537568761</v>
       </c>
       <c r="C27">
-        <v>1.446268749666392</v>
+        <v>0.003044785806551986</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.256536311741849</v>
+        <v>-1.157570404491341</v>
       </c>
       <c r="C28">
-        <v>1.553705849734875</v>
+        <v>-1.519522723979212</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.7992165485564741</v>
+        <v>0.5105977407425887</v>
       </c>
       <c r="C29">
-        <v>-0.4177004328782315</v>
+        <v>-1.108324829763471</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>2.016790527999998</v>
+        <v>-1.958062116589383</v>
       </c>
       <c r="C30">
-        <v>1.642273440096182</v>
+        <v>0.4457066490404954</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.126447731369716</v>
+        <v>0.9934108409907324</v>
       </c>
       <c r="C31">
-        <v>0.3375242670296233</v>
+        <v>-0.1081703454347042</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.1970119458019039</v>
+        <v>-0.74836242177791</v>
       </c>
       <c r="C32">
-        <v>-0.09479564404805604</v>
+        <v>-0.410636305089469</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.08080056267025791</v>
+        <v>1.435174427474009</v>
       </c>
       <c r="C33">
-        <v>-1.794770918940284</v>
+        <v>1.692865528334795</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-1.599158370229429</v>
+        <v>-2.131135872935858</v>
       </c>
       <c r="C34">
-        <v>-1.608676371655254</v>
+        <v>-0.3494025714390891</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.286804851901339</v>
+        <v>-1.438176191312895</v>
       </c>
       <c r="C35">
-        <v>1.170487116812818</v>
+        <v>-0.9685531407486903</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.926398733531283</v>
+        <v>-0.8598161181803081</v>
       </c>
       <c r="C36">
-        <v>0.4630695600990153</v>
+        <v>0.4051025331182786</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.4779561916511323</v>
+        <v>0.8420989119055985</v>
       </c>
       <c r="C37">
-        <v>-1.652894430898206</v>
+        <v>0.8878268394040189</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.07137877274145832</v>
+        <v>0.7749156572934679</v>
       </c>
       <c r="C38">
-        <v>0.09141695000396098</v>
+        <v>1.180792370415668</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.1951475946538249</v>
+        <v>-0.7298495774540148</v>
       </c>
       <c r="C39">
-        <v>1.423448168059895</v>
+        <v>0.9001261176106532</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.473709009082885</v>
+        <v>-0.5966878496798863</v>
       </c>
       <c r="C40">
-        <v>0.1689214155679168</v>
+        <v>1.198598437449088</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.1124788110281342</v>
+        <v>-1.287755040343741</v>
       </c>
       <c r="C41">
-        <v>2.006715860035234</v>
+        <v>-1.071720529653544</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>1.561934185996829</v>
+        <v>-0.8997602644402884</v>
       </c>
       <c r="C42">
-        <v>-0.6029137025033169</v>
+        <v>-0.8280858096049388</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.2788983083250345</v>
+        <v>-0.1526686085090432</v>
       </c>
       <c r="C43">
-        <v>2.106700960068094</v>
+        <v>1.493633163147646</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.642474000028229</v>
+        <v>-0.6897752352585939</v>
       </c>
       <c r="C44">
-        <v>2.061240482474958</v>
+        <v>0.01103304851900611</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.1119755872134413</v>
+        <v>1.381089254753248</v>
       </c>
       <c r="C45">
-        <v>-1.063449847848199</v>
+        <v>-0.549087915410845</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.3099586332159239</v>
+        <v>-1.003924676579926</v>
       </c>
       <c r="C46">
-        <v>0.704987740835947</v>
+        <v>0.1119779445514278</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.9232146453980222</v>
+        <v>-0.5294565380347421</v>
       </c>
       <c r="C47">
-        <v>-0.2517342195819529</v>
+        <v>1.890755910538471</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.228069713880792</v>
+        <v>0.1933392375403806</v>
       </c>
       <c r="C48">
-        <v>-1.4071209959823</v>
+        <v>1.42433413063246</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-1.164676682666723</v>
+        <v>0.9413463981842785</v>
       </c>
       <c r="C49">
-        <v>-0.2134568921292762</v>
+        <v>-0.3676898427737154</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.590232559615857</v>
+        <v>-0.3448815299180479</v>
       </c>
       <c r="C50">
-        <v>1.821632378700193</v>
+        <v>0.2800319099505622</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.6961392898128304</v>
+        <v>-0.7149931435170248</v>
       </c>
       <c r="C51">
-        <v>1.670135132532837</v>
+        <v>1.907354088984767</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-2.120856336128438</v>
+        <v>0.9969454540741056</v>
       </c>
       <c r="C52">
-        <v>1.210350286548731</v>
+        <v>0.7258199543384204</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.4601568996824417</v>
+        <v>0.02398437762626169</v>
       </c>
       <c r="C53">
-        <v>0.1746550299460551</v>
+        <v>-0.50200324108628</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.3391178725922242</v>
+        <v>0.4731299721826125</v>
       </c>
       <c r="C54">
-        <v>1.091949563473463</v>
+        <v>1.110129806822887</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.03965924683044035</v>
+        <v>-0.8248663561295924</v>
       </c>
       <c r="C55">
-        <v>0.5176893339794344</v>
+        <v>-1.830185296791964</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-1.135077326882171</v>
+        <v>2.62386612911759</v>
       </c>
       <c r="C56">
-        <v>1.222827442751682</v>
+        <v>1.836191664331386</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9341998415876733</v>
+        <v>-0.5953721519676255</v>
       </c>
       <c r="C57">
-        <v>0.1078971323915317</v>
+        <v>-0.5037353172304302</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-1.029696755396622</v>
+        <v>1.110154507485565</v>
       </c>
       <c r="C58">
-        <v>-0.3654161466916077</v>
+        <v>0.3618399353201521</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>-1.234848596839058</v>
+        <v>0.607002118487687</v>
       </c>
       <c r="C59">
-        <v>-0.1991863301751828</v>
+        <v>0.3852732964343372</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-1.340843736215773</v>
+        <v>0.304830152425327</v>
       </c>
       <c r="C60">
-        <v>2.04725883108544</v>
+        <v>0.4880577497267661</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-1.41009033421381</v>
+        <v>-1.500933319594189</v>
       </c>
       <c r="C61">
-        <v>-0.8320727658296512</v>
+        <v>-0.1831220663592952</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.1261298261416459</v>
+        <v>-0.06828759813437489</v>
       </c>
       <c r="C62">
-        <v>0.3508316620937655</v>
+        <v>0.6679051656013055</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.5206420244484427</v>
+        <v>0.840406009957283</v>
       </c>
       <c r="C63">
-        <v>1.569912395258118</v>
+        <v>0.6893179423457808</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.3300258923880263</v>
+        <v>-0.03588164376462533</v>
       </c>
       <c r="C64">
-        <v>2.27715080609129</v>
+        <v>0.5505143561739567</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.1695132823044142</v>
+        <v>-1.750158530961963</v>
       </c>
       <c r="C65">
-        <v>1.459201795564867</v>
+        <v>-2.805514582437456</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-0.3039796888192907</v>
+        <v>0.6686746936965196</v>
       </c>
       <c r="C66">
-        <v>-0.647442911304372</v>
+        <v>0.391181999500907</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>1.399335592493518</v>
+        <v>-0.1767251789423312</v>
       </c>
       <c r="C67">
-        <v>-0.2789691097199445</v>
+        <v>-0.5856220413196166</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-2.936588044210001</v>
+        <v>-0.6088414335017686</v>
       </c>
       <c r="C68">
-        <v>-0.7915540523742022</v>
+        <v>-1.514854113340455</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.2986985373277988</v>
+        <v>0.5903029212778134</v>
       </c>
       <c r="C69">
-        <v>0.2531134536122908</v>
+        <v>0.03937245162597416</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.07303510497907269</v>
+        <v>0.3755274602900007</v>
       </c>
       <c r="C70">
-        <v>0.3658637173112329</v>
+        <v>0.3648050730492512</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.9400423629386033</v>
+        <v>-1.762982231087067</v>
       </c>
       <c r="C71">
-        <v>0.1042914620740947</v>
+        <v>-1.257202778639658</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-1.33747772483378</v>
+        <v>0.1693759238371985</v>
       </c>
       <c r="C72">
-        <v>-0.5002283333210612</v>
+        <v>-0.8399847284726948</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>1.262468757796807</v>
+        <v>-0.0007859125062208706</v>
       </c>
       <c r="C73">
-        <v>1.458792569116113</v>
+        <v>-0.8859038754016603</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.3828743004400599</v>
+        <v>-1.63012998903584</v>
       </c>
       <c r="C74">
-        <v>0.6099727102030146</v>
+        <v>-2.060824388090609</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-2.939258003058004</v>
+        <v>1.713425028727145</v>
       </c>
       <c r="C75">
-        <v>-0.612190325253251</v>
+        <v>-0.05611719268380055</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>-0.9035305153426855</v>
+        <v>0.8439392347653975</v>
       </c>
       <c r="C76">
-        <v>-0.1019226035623002</v>
+        <v>1.310267506815078</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.08085959507082641</v>
+        <v>0.3680602979882983</v>
       </c>
       <c r="C77">
-        <v>-0.3880833129908612</v>
+        <v>-1.655832056129144</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.06563206666604159</v>
+        <v>-0.7192475528657866</v>
       </c>
       <c r="C78">
-        <v>1.273209927388847</v>
+        <v>-3.408252631111992</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.2589467073052634</v>
+        <v>0.1450288587121449</v>
       </c>
       <c r="C79">
-        <v>-1.04925215774706</v>
+        <v>-0.4841037170509208</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>-0.8633976754288221</v>
+        <v>-0.4802854820661546</v>
       </c>
       <c r="C80">
-        <v>-0.7624872838696466</v>
+        <v>0.2035320476169198</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-0.6990528085624067</v>
+        <v>1.26673461785596</v>
       </c>
       <c r="C81">
-        <v>0.3239579620920334</v>
+        <v>0.3553022118609508</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>1.402405066522386</v>
+        <v>0.5269294787187796</v>
       </c>
       <c r="C82">
-        <v>-1.162398957693136</v>
+        <v>0.4113742619020575</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-0.3872366293860971</v>
+        <v>1.640059980404864</v>
       </c>
       <c r="C83">
-        <v>0.3633421258379998</v>
+        <v>-0.1764389579026517</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.03624921231731446</v>
+        <v>-0.746785929114508</v>
       </c>
       <c r="C84">
-        <v>-0.7391773139389198</v>
+        <v>0.7810012450824779</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.37514266919462</v>
+        <v>0.4166284082345082</v>
       </c>
       <c r="C85">
-        <v>-0.5309732879751915</v>
+        <v>-0.3819435213584084</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.313123554131162</v>
+        <v>-1.052756041208776</v>
       </c>
       <c r="C86">
-        <v>-1.135975267804849</v>
+        <v>0.3289112051190055</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.08842830268469284</v>
+        <v>-0.3438697498366535</v>
       </c>
       <c r="C87">
-        <v>0.2910356568818664</v>
+        <v>-2.314068970572234</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.05180185964139196</v>
+        <v>-0.4664874904385672</v>
       </c>
       <c r="C88">
-        <v>1.376644991845221</v>
+        <v>0.9584706498713551</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.3834668165453727</v>
+        <v>0.8410560984080555</v>
       </c>
       <c r="C89">
-        <v>-1.015117065296936</v>
+        <v>0.805221445289299</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-0.2313445334094724</v>
+        <v>0.9385345271545771</v>
       </c>
       <c r="C90">
-        <v>0.5412484776517411</v>
+        <v>-1.414650490253005</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.8952068334028139</v>
+        <v>0.4639578083261071</v>
       </c>
       <c r="C91">
-        <v>0.03458268139509267</v>
+        <v>-0.2305595018983822</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.7310795800925799</v>
+        <v>-0.2912378756803</v>
       </c>
       <c r="C92">
-        <v>-0.7356187323480461</v>
+        <v>0.03290888105979337</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.5178867211856724</v>
+        <v>-0.0190023219620281</v>
       </c>
       <c r="C93">
-        <v>-0.6415370995015398</v>
+        <v>-1.165678038692549</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.3909311682546411</v>
+        <v>-0.4777627836727225</v>
       </c>
       <c r="C94">
-        <v>-0.2897058579372015</v>
+        <v>-0.2021264189810133</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.5578938816847725</v>
+        <v>-1.841238065260715</v>
       </c>
       <c r="C95">
-        <v>1.629667919560665</v>
+        <v>-1.338603001539966</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.6845971216678778</v>
+        <v>-0.3584278139126113</v>
       </c>
       <c r="C96">
-        <v>-1.64717580246625</v>
+        <v>-0.2757253266527055</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.5858430221610049</v>
+        <v>0.3198148511958618</v>
       </c>
       <c r="C97">
-        <v>-0.7938556737396955</v>
+        <v>-0.2206382378361229</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-0.5259591673044338</v>
+        <v>-0.8975985837307003</v>
       </c>
       <c r="C98">
-        <v>-0.2344289851294327</v>
+        <v>-2.730656116439596</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-0.064569991335968</v>
+        <v>-1.326677900704334</v>
       </c>
       <c r="C99">
-        <v>0.5291432447484484</v>
+        <v>-0.2974049030571625</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.3528509829293118</v>
+        <v>-1.769388215925265</v>
       </c>
       <c r="C100">
-        <v>-0.4310970980414639</v>
+        <v>1.087902240768114</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>-0.2265138289970351</v>
+        <v>1.091756310827869</v>
       </c>
       <c r="C101">
-        <v>-0.7878657396187466</v>
+        <v>-0.6737403163446556</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-0.2360563702762305</v>
+      </c>
+      <c r="C102">
+        <v>-0.3808993619547266</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.07206637800338253</v>
+      </c>
+      <c r="C103">
+        <v>0.9276609569445491</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-1.18018012613851</v>
+      </c>
+      <c r="C104">
+        <v>-0.7139612491987211</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>-0.4996207914130775</v>
+      </c>
+      <c r="C105">
+        <v>-2.089307420227467</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>0.02044427786232417</v>
+      </c>
+      <c r="C106">
+        <v>-0.5581243342877815</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-0.120706068980103</v>
+      </c>
+      <c r="C107">
+        <v>0.82063329615506</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>1.178400428415401</v>
+      </c>
+      <c r="C108">
+        <v>-0.3341989599105493</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>-0.4839735319170653</v>
+      </c>
+      <c r="C109">
+        <v>1.244436524986382</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-2.466507242432791</v>
+      </c>
+      <c r="C110">
+        <v>-0.4580087579930785</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.4212352498211512</v>
+      </c>
+      <c r="C111">
+        <v>-1.022758507123585</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.2388616004854686</v>
+      </c>
+      <c r="C112">
+        <v>-0.4025030317190673</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.1787187396627261</v>
+      </c>
+      <c r="C113">
+        <v>-1.29680843339462</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-0.2617168155676938</v>
+      </c>
+      <c r="C114">
+        <v>-0.4471032788278798</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-1.113222065871722</v>
+      </c>
+      <c r="C115">
+        <v>0.2921563028564987</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-1.370666383620255</v>
+      </c>
+      <c r="C116">
+        <v>-1.287772154059118</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>0.4488735176604348</v>
+      </c>
+      <c r="C117">
+        <v>-0.7930771252905682</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.629594917667783</v>
+      </c>
+      <c r="C118">
+        <v>-0.742893524602769</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-1.565884815758384</v>
+      </c>
+      <c r="C119">
+        <v>-2.361692747880348</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.5659084918824822</v>
+      </c>
+      <c r="C120">
+        <v>0.504773230501825</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.5350069960087827</v>
+      </c>
+      <c r="C121">
+        <v>-1.104086335478344</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.1024789287039781</v>
+      </c>
+      <c r="C122">
+        <v>0.006602835310854441</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.2000866083123822</v>
+      </c>
+      <c r="C123">
+        <v>-1.281658259458704</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.2647654300688176</v>
+      </c>
+      <c r="C124">
+        <v>0.9664505535968343</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>-0.271793343146115</v>
+      </c>
+      <c r="C125">
+        <v>-0.1977968574057093</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>1.184512697501138</v>
+      </c>
+      <c r="C126">
+        <v>0.3799248181894058</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-1.091799984710006</v>
+      </c>
+      <c r="C127">
+        <v>-0.9003127820968649</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.1889970475624022</v>
+      </c>
+      <c r="C128">
+        <v>-0.4282994352873509</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.07829886395430749</v>
+      </c>
+      <c r="C129">
+        <v>-0.2714542756426275</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.5120649810565135</v>
+      </c>
+      <c r="C130">
+        <v>-1.524011516961131</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-0.09270344493526606</v>
+      </c>
+      <c r="C131">
+        <v>1.227729942154976</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-2.077359581591007</v>
+      </c>
+      <c r="C132">
+        <v>-1.195200804848007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.3548968593707918</v>
+      </c>
+      <c r="C133">
+        <v>-0.8295959045404799</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>0.1208748203730788</v>
+      </c>
+      <c r="C134">
+        <v>-1.187035737823816</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.4642976819980897</v>
+      </c>
+      <c r="C135">
+        <v>-1.297096020523304</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-0.5221048654007362</v>
+      </c>
+      <c r="C136">
+        <v>-1.747965858099917</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>0.425087559802249</v>
+      </c>
+      <c r="C137">
+        <v>0.4823842790385431</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>1.467542857480151</v>
+      </c>
+      <c r="C138">
+        <v>0.3145741411652729</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>1.552827951953051</v>
+      </c>
+      <c r="C139">
+        <v>0.8850522701332117</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>0.5778786416823242</v>
+      </c>
+      <c r="C140">
+        <v>-0.7310109776688605</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1.006096569273202</v>
+      </c>
+      <c r="C141">
+        <v>-1.308578587642292</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>-0.8394380530662348</v>
+      </c>
+      <c r="C142">
+        <v>-0.25780441440319</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-0.2705994792359226</v>
+      </c>
+      <c r="C143">
+        <v>-0.4151968642033646</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.4553095265328734</v>
+      </c>
+      <c r="C144">
+        <v>-0.6818543511823048</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-1.09219134789512</v>
+      </c>
+      <c r="C145">
+        <v>0.3618455547161398</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1.405948374558779</v>
+      </c>
+      <c r="C146">
+        <v>-2.337253468106382</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-1.579398717583758</v>
+      </c>
+      <c r="C147">
+        <v>-1.47198918753932</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.1389185295831778</v>
+      </c>
+      <c r="C148">
+        <v>-0.124212375945386</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>1.159674384669531</v>
+      </c>
+      <c r="C149">
+        <v>-0.6418721340496332</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>0.125213807766796</v>
+      </c>
+      <c r="C150">
+        <v>-0.437323184728855</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>2.000633226198636</v>
+      </c>
+      <c r="C151">
+        <v>2.188055333907053</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-0.003661362147612097</v>
+      </c>
+      <c r="C152">
+        <v>0.3989706169827795</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>-0.1650796095128268</v>
+      </c>
+      <c r="C153">
+        <v>0.4823476411994454</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-0.920116532229282</v>
+      </c>
+      <c r="C154">
+        <v>-0.1204580924038999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.3412043896010355</v>
+      </c>
+      <c r="C155">
+        <v>-0.9262514835227044</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>-0.3081276383464524</v>
+      </c>
+      <c r="C156">
+        <v>-0.3466959733055729</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.08005908423455836</v>
+      </c>
+      <c r="C157">
+        <v>-0.5920606536662953</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.9768180233096855</v>
+      </c>
+      <c r="C158">
+        <v>1.249916782254278</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>0.6922404799000016</v>
+      </c>
+      <c r="C159">
+        <v>0.6929223973799153</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.6906693622294233</v>
+      </c>
+      <c r="C160">
+        <v>1.44416219057281</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.8807255084441885</v>
+      </c>
+      <c r="C161">
+        <v>0.1607044180252907</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-0.559718460587215</v>
+      </c>
+      <c r="C162">
+        <v>-0.06811935091384647</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.3063982592601266</v>
+      </c>
+      <c r="C163">
+        <v>0.504172041539487</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>-0.8839704873673415</v>
+      </c>
+      <c r="C164">
+        <v>0.9433787020125621</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-1.5052468656625</v>
+      </c>
+      <c r="C165">
+        <v>0.3638795236119265</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.4596171982690523</v>
+      </c>
+      <c r="C166">
+        <v>0.0700138608579398</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.01304172198366482</v>
+      </c>
+      <c r="C167">
+        <v>-0.1157649403839827</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>-1.187980197608241</v>
+      </c>
+      <c r="C168">
+        <v>-0.8920533441448328</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>1.516698120008842</v>
+      </c>
+      <c r="C169">
+        <v>2.602922492985098</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>2.251280881799449</v>
+      </c>
+      <c r="C170">
+        <v>0.06209990504763019</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.535248400506072</v>
+      </c>
+      <c r="C171">
+        <v>-1.217581536805193</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>-0.3120840426272696</v>
+      </c>
+      <c r="C172">
+        <v>0.5349046109719312</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-0.003076484391032793</v>
+      </c>
+      <c r="C173">
+        <v>0.7084050094867761</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>1.31633542427186</v>
+      </c>
+      <c r="C174">
+        <v>0.6878515715998514</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.6173870720203902</v>
+      </c>
+      <c r="C175">
+        <v>1.247423429564114</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-0.5739225440710832</v>
+      </c>
+      <c r="C176">
+        <v>-0.4208733216368328</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-0.9985720251467595</v>
+      </c>
+      <c r="C177">
+        <v>-0.2751122984219586</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>-0.2937938435215192</v>
+      </c>
+      <c r="C178">
+        <v>1.22549457468315</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>1.126424522976029</v>
+      </c>
+      <c r="C179">
+        <v>1.642693986142306</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.6413078149159063</v>
+      </c>
+      <c r="C180">
+        <v>-1.484500689110611</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>-0.03107305741040847</v>
+      </c>
+      <c r="C181">
+        <v>-0.2105039617421401</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-1.421704257426954</v>
+      </c>
+      <c r="C182">
+        <v>-0.4187224018941081</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-1.566331485534254</v>
+      </c>
+      <c r="C183">
+        <v>-0.5669729219170722</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.7770172028085739</v>
+      </c>
+      <c r="C184">
+        <v>0.4133322524702137</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>0.4047927760162562</v>
+      </c>
+      <c r="C185">
+        <v>-0.4379911067939148</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1.012062074284336</v>
+      </c>
+      <c r="C186">
+        <v>1.394805178259109</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-1.047553031386877</v>
+      </c>
+      <c r="C187">
+        <v>0.4436646257053333</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-0.7324792975683673</v>
+      </c>
+      <c r="C188">
+        <v>-0.8637852324769564</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.4286922050634745</v>
+      </c>
+      <c r="C189">
+        <v>0.03998569666436308</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>-0.1372826970720923</v>
+      </c>
+      <c r="C190">
+        <v>-0.152418275428157</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>0.3716982582862872</v>
+      </c>
+      <c r="C191">
+        <v>0.9305443398411224</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.1835060473045072</v>
+      </c>
+      <c r="C192">
+        <v>0.5399207764577507</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.1957213302533934</v>
+      </c>
+      <c r="C193">
+        <v>-1.423560580049683</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.3529245277455503</v>
+      </c>
+      <c r="C194">
+        <v>-0.2290994138627895</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>1.886426506739962</v>
+      </c>
+      <c r="C195">
+        <v>0.5906940229878064</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.778581132503014</v>
+      </c>
+      <c r="C196">
+        <v>-1.55490209945248</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>-1.276789201209408</v>
+      </c>
+      <c r="C197">
+        <v>0.1792941828177766</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>0.5826079158014296</v>
+      </c>
+      <c r="C198">
+        <v>0.620155638969586</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>1.226618834666381</v>
+      </c>
+      <c r="C199">
+        <v>-0.2966534354515608</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-0.6897154383495148</v>
+      </c>
+      <c r="C200">
+        <v>-0.1687083216226027</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-2.644256042607968</v>
+      </c>
+      <c r="C201">
+        <v>-0.1345712112011193</v>
       </c>
     </row>
   </sheetData>
